--- a/ip_fqdn.xlsx
+++ b/ip_fqdn.xlsx
@@ -19,6 +19,20 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -114,9 +128,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultColWidth="8.4296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
